--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/sumario_modelos.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/sumario_modelos.xlsx
@@ -482,7 +482,7 @@
         <v>-44.37090636530863</v>
       </c>
       <c r="G2" t="n">
-        <v>-47.55177534156072</v>
+        <v>-47.55177534156071</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -659,10 +659,10 @@
         <v>-49.34872312736437</v>
       </c>
       <c r="F8" t="n">
-        <v>-43.99130174756713</v>
+        <v>-43.99130174756714</v>
       </c>
       <c r="G8" t="n">
-        <v>-47.17217072381921</v>
+        <v>-47.17217072381922</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
